--- a/docs/StructureDefinition-fr-core-organization.xlsx
+++ b/docs/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-03T19:04:37+02:00</t>
+    <t>2025-11-02T16:31:57+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,7 +364,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -961,7 +961,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -1032,7 +1032,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1359,11 +1359,11 @@
     <col min="2" max="2" width="33.609375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.91796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.25" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.57421875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.14453125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="5.62890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.2421875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.640625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.58984375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.17578125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="130.828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1374,26 +1374,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.54296875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.1953125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="15.7578125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.34765625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.65234375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.05078125" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.32421875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="15.765625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="48.01953125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.50390625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.41015625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="18.95703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="18.9921875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.42578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="30" max="30" width="14.30859375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.7890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="31.2109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.86328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.23828125" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="8.828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.2265625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="27.2109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="44.828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="192.56640625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="30.76171875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="30.8359375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-fr-core-organization.xlsx
+++ b/docs/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-02T16:31:57+01:00</t>
+    <t>2025-11-02T18:22:16+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
